--- a/data/trans_orig/P1409-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1409-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2012</t>
+          <t>Población con diagnóstico de asma en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>16753</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37574</t>
+          <t>37028</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30257</t>
+          <t>30928</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57731</t>
+          <t>57133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51741</t>
+          <t>52647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86191</t>
+          <t>85064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>937069</t>
+          <t>937615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>957843</t>
+          <t>957890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1278883</t>
+          <t>1279481</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1306357</t>
+          <t>1305686</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2225066</t>
+          <t>2226193</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2259516</t>
+          <t>2258610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22468</t>
+          <t>22693</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44438</t>
+          <t>45563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29700</t>
+          <t>29120</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56726</t>
+          <t>54827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57451</t>
+          <t>56940</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91085</t>
+          <t>91444</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1919519</t>
+          <t>1918394</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1941489</t>
+          <t>1941264</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1697866</t>
+          <t>1699765</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1724892</t>
+          <t>1725472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3627464</t>
+          <t>3627105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3661098</t>
+          <t>3661609</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16228</t>
+          <t>16428</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31661</t>
+          <t>32639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>464953</t>
+          <t>464753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>478243</t>
+          <t>478255</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437494</t>
+          <t>437489</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>452260</t>
+          <t>451731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>908152</t>
+          <t>907174</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>926895</t>
+          <t>927471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49294</t>
+          <t>50948</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84565</t>
+          <t>83159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77807</t>
+          <t>77103</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116711</t>
+          <t>117618</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138043</t>
+          <t>137717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189629</t>
+          <t>187542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3335217</t>
+          <t>3336623</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3370488</t>
+          <t>3368834</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3433126</t>
+          <t>3432219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3472030</t>
+          <t>3472734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6779990</t>
+          <t>6782077</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6831576</t>
+          <t>6831902</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2016</t>
+          <t>Población con diagnóstico de asma en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>33861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31481</t>
+          <t>30359</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59371</t>
+          <t>60749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52575</t>
+          <t>52664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85322</t>
+          <t>87457</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>720912</t>
+          <t>720486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>738327</t>
+          <t>738639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>935289</t>
+          <t>933911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>963179</t>
+          <t>964301</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1663685</t>
+          <t>1661550</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1696432</t>
+          <t>1696343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39877</t>
+          <t>39619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68150</t>
+          <t>68689</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59977</t>
+          <t>59640</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94347</t>
+          <t>95281</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106650</t>
+          <t>106705</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151014</t>
+          <t>153820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2008235</t>
+          <t>2007696</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2036508</t>
+          <t>2036766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1893953</t>
+          <t>1893019</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1928323</t>
+          <t>1928660</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3913671</t>
+          <t>3910865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3958035</t>
+          <t>3957980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18498</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13652</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31116</t>
+          <t>30619</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>19835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42082</t>
+          <t>42840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528388</t>
+          <t>528668</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542296</t>
+          <t>542707</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>518024</t>
+          <t>518521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>535488</t>
+          <t>536303</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053945</t>
+          <t>1053187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1076954</t>
+          <t>1076192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68994</t>
+          <t>68290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106424</t>
+          <t>106886</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116357</t>
+          <t>117587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162866</t>
+          <t>165283</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>195115</t>
+          <t>198888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>259013</t>
+          <t>257075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3271194</t>
+          <t>3270732</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3308624</t>
+          <t>3309328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3369234</t>
+          <t>3366817</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3415743</t>
+          <t>3414513</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6650705</t>
+          <t>6652643</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6714603</t>
+          <t>6710830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de asma en 2023</t>
+          <t>Población con diagnóstico de asma en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19142</t>
+          <t>18106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>37484</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37697</t>
+          <t>37362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57727</t>
+          <t>57233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60479</t>
+          <t>62063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88778</t>
+          <t>88300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>474124</t>
+          <t>475136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493478</t>
+          <t>494514</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>693704</t>
+          <t>694198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>713734</t>
+          <t>714069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1175274</t>
+          <t>1175752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1203573</t>
+          <t>1201989</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50617</t>
+          <t>51065</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102981</t>
+          <t>106029</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80886</t>
+          <t>80719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>389398</t>
+          <t>378212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>150711</t>
+          <t>152782</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>461479</t>
+          <t>498205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2185694</t>
+          <t>2182646</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2238058</t>
+          <t>2237610</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1846679</t>
+          <t>1857865</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2155191</t>
+          <t>2155358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4063274</t>
+          <t>4026548</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4374042</t>
+          <t>4371971</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36901</t>
+          <t>35911</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19203</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35780</t>
+          <t>34154</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>37249</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65010</t>
+          <t>65094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609722</t>
+          <t>610712</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631732</t>
+          <t>631842</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>624090</t>
+          <t>625716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>640667</t>
+          <t>641044</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1241484</t>
+          <t>1241400</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1268447</t>
+          <t>1269245</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94993</t>
+          <t>97110</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155217</t>
+          <t>160294</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156451</t>
+          <t>153227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>528600</t>
+          <t>456730</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275993</t>
+          <t>269990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>663957</t>
+          <t>631558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3292702</t>
+          <t>3287625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3352926</t>
+          <t>3350809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3118779</t>
+          <t>3190649</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3490928</t>
+          <t>3494152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6431341</t>
+          <t>6463740</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6819305</t>
+          <t>6825308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1409-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1409-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16753</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37028</t>
+          <t>36355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30928</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57133</t>
+          <t>57617</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52647</t>
+          <t>52550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85064</t>
+          <t>87139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>937615</t>
+          <t>938288</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>957890</t>
+          <t>958477</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1279481</t>
+          <t>1278997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1305686</t>
+          <t>1306861</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2226193</t>
+          <t>2224118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2258610</t>
+          <t>2258707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45563</t>
+          <t>45175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29120</t>
+          <t>29925</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54827</t>
+          <t>55350</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56940</t>
+          <t>57905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91444</t>
+          <t>92286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1918394</t>
+          <t>1918782</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1941264</t>
+          <t>1941085</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1699765</t>
+          <t>1699242</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1725472</t>
+          <t>1724667</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3627105</t>
+          <t>3626263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3661609</t>
+          <t>3660644</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16428</t>
+          <t>16707</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12342</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32639</t>
+          <t>32893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>464753</t>
+          <t>464474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>478255</t>
+          <t>478292</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>437489</t>
+          <t>437796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>451731</t>
+          <t>452194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>907174</t>
+          <t>906920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>927471</t>
+          <t>926511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50948</t>
+          <t>50997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83159</t>
+          <t>82718</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77103</t>
+          <t>78193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117618</t>
+          <t>116828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137717</t>
+          <t>138651</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187542</t>
+          <t>188861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3336623</t>
+          <t>3337064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3368834</t>
+          <t>3368785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3432219</t>
+          <t>3433009</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3472734</t>
+          <t>3471644</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6782077</t>
+          <t>6780758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6831902</t>
+          <t>6830968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15708</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33861</t>
+          <t>33851</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30359</t>
+          <t>32196</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60749</t>
+          <t>60276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52664</t>
+          <t>52344</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87457</t>
+          <t>86120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>720486</t>
+          <t>720496</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>738639</t>
+          <t>738720</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>933911</t>
+          <t>934384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>964301</t>
+          <t>962464</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1661550</t>
+          <t>1662887</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1696343</t>
+          <t>1696663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39619</t>
+          <t>40141</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68689</t>
+          <t>69996</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59640</t>
+          <t>61071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95281</t>
+          <t>94565</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106705</t>
+          <t>108528</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153820</t>
+          <t>154621</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2007696</t>
+          <t>2006389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2036766</t>
+          <t>2036244</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1893019</t>
+          <t>1893735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1928660</t>
+          <t>1927229</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3910865</t>
+          <t>3910064</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3957980</t>
+          <t>3956157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>18883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30619</t>
+          <t>30808</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19835</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42840</t>
+          <t>42297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528668</t>
+          <t>528003</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542707</t>
+          <t>542243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>518521</t>
+          <t>518332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>536303</t>
+          <t>535966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053187</t>
+          <t>1053730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1076192</t>
+          <t>1076158</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68290</t>
+          <t>68738</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106886</t>
+          <t>105133</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117587</t>
+          <t>118293</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165283</t>
+          <t>167710</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198888</t>
+          <t>198522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>257075</t>
+          <t>256899</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3270732</t>
+          <t>3272485</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3309328</t>
+          <t>3308880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3366817</t>
+          <t>3364390</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3414513</t>
+          <t>3413807</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6652643</t>
+          <t>6652819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6710830</t>
+          <t>6711196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26897</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37484</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>46765</t>
+          <t>49714</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37362</t>
+          <t>39597</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57233</t>
+          <t>60648</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>73662</t>
+          <t>77476</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62063</t>
+          <t>65385</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88300</t>
+          <t>93323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>485723</t>
+          <t>548381</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>475136</t>
+          <t>537425</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494514</t>
+          <t>556643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>704666</t>
+          <t>769765</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>694198</t>
+          <t>758831</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>714069</t>
+          <t>779882</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1190390</t>
+          <t>1318147</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1175752</t>
+          <t>1302300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1201989</t>
+          <t>1330238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512620</t>
+          <t>576143</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512620</t>
+          <t>576143</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512620</t>
+          <t>576143</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751431</t>
+          <t>819479</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751431</t>
+          <t>819479</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751431</t>
+          <t>819479</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1264052</t>
+          <t>1395623</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1264052</t>
+          <t>1395623</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1264052</t>
+          <t>1395623</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>76587</t>
+          <t>78652</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51065</t>
+          <t>58648</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106029</t>
+          <t>104534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>156417</t>
+          <t>95148</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80719</t>
+          <t>77576</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>378212</t>
+          <t>113032</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>233005</t>
+          <t>173800</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152782</t>
+          <t>148266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>498205</t>
+          <t>204992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2212088</t>
+          <t>2150056</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2182646</t>
+          <t>2124174</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2237610</t>
+          <t>2170060</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2079660</t>
+          <t>2074507</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1857865</t>
+          <t>2056623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2155358</t>
+          <t>2092079</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4291748</t>
+          <t>4224564</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4026548</t>
+          <t>4193372</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4371971</t>
+          <t>4250098</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288675</t>
+          <t>2228708</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288675</t>
+          <t>2228708</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288675</t>
+          <t>2228708</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236077</t>
+          <t>2169655</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236077</t>
+          <t>2169655</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236077</t>
+          <t>2169655</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524753</t>
+          <t>4398364</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524753</t>
+          <t>4398364</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524753</t>
+          <t>4398364</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23215</t>
+          <t>28880</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>18041</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35911</t>
+          <t>43784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26165</t>
+          <t>32835</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34154</t>
+          <t>43760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49380</t>
+          <t>61715</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37249</t>
+          <t>47937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65094</t>
+          <t>82023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>623408</t>
+          <t>682707</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610712</t>
+          <t>667803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631842</t>
+          <t>693546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>633705</t>
+          <t>700905</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>625716</t>
+          <t>689980</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641044</t>
+          <t>709212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1257114</t>
+          <t>1383612</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1241400</t>
+          <t>1363304</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1269245</t>
+          <t>1397390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659870</t>
+          <t>733740</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659870</t>
+          <t>733740</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659870</t>
+          <t>733740</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306494</t>
+          <t>1445327</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306494</t>
+          <t>1445327</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306494</t>
+          <t>1445327</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>126700</t>
+          <t>135294</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97110</t>
+          <t>110697</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160294</t>
+          <t>166222</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,22 +4997,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>229348</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153227</t>
+          <t>156502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>456730</t>
+          <t>200575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>356047</t>
+          <t>312990</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>269990</t>
+          <t>280931</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>631558</t>
+          <t>354577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3321219</t>
+          <t>3381145</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3287625</t>
+          <t>3350217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3350809</t>
+          <t>3405742</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,27 +5110,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3418031</t>
+          <t>3545179</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3190649</t>
+          <t>3522300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3494152</t>
+          <t>3566373</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6739251</t>
+          <t>6926323</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6463740</t>
+          <t>6884736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6825308</t>
+          <t>6958382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3447919</t>
+          <t>3516439</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3447919</t>
+          <t>3516439</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3447919</t>
+          <t>3516439</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3647379</t>
+          <t>3722875</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3647379</t>
+          <t>3722875</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3647379</t>
+          <t>3722875</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7095298</t>
+          <t>7239313</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7095298</t>
+          <t>7239313</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7095298</t>
+          <t>7239313</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
